--- a/data/hrm_sync_actual.xlsx
+++ b/data/hrm_sync_actual.xlsx
@@ -70,175 +70,457 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Lớn hơn KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 2</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
     <t>02516134</t>
   </si>
   <si>
     <t>Ngô Xuân Nghĩa</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>Thực hiện dự án cải tiến</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
   </si>
   <si>
     <t>thực hiện dự án cải tiến</t>
   </si>
   <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02224288</t>
-  </si>
-  <si>
-    <t>Võ Văn Dương</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Lớn hơn KH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gian tiếp</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>01921560</t>
-  </si>
-  <si>
-    <t>Trần Quang Hiệu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
   </si>
   <si>
     <t>02241656</t>
@@ -247,58 +529,28 @@
     <t>Lương Trọng Ân</t>
   </si>
   <si>
+    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
     <t>tăng ca sản xuất ca2</t>
   </si>
   <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
+    <t>15/09/2026 12:30:00</t>
   </si>
   <si>
     <t>08/09/2026 16:30:00</t>
@@ -307,100 +559,16 @@
     <t>08/09/2026 19:30:00</t>
   </si>
   <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:00:00</t>
   </si>
   <si>
     <t>02325301</t>
@@ -409,129 +577,6 @@
     <t>Cao Thế Mỹ</t>
   </si>
   <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
     <t>02645269</t>
   </si>
   <si>
@@ -544,58 +589,37 @@
     <t>10/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
     <t>16/09/2026 20:30:00</t>
   </si>
   <si>
     <t>16/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
     <t>18/09/2026 20:30:00</t>
   </si>
   <si>
     <t>18/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
     <t>15/09/2026 20:30:00</t>
   </si>
   <si>
     <t>15/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
+    <t>11/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
   </si>
   <si>
     <t>14/09/2026 20:30:00</t>
@@ -604,54 +628,27 @@
     <t>14/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
     <t>lắp rack bobin tại xưởng 3</t>
   </si>
   <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
     <t>02325374</t>
   </si>
   <si>
     <t>Trương Văn Tình</t>
   </si>
   <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
     <t>Tăng ca lắp rack xưởng 3</t>
   </si>
   <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
     <t>02021742</t>
   </si>
   <si>
@@ -682,6 +679,12 @@
     <t>Tăng ca hổ trợ sản xuất (HC)</t>
   </si>
   <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
     <t>02325365</t>
   </si>
   <si>
@@ -703,12 +706,6 @@
     <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
   </si>
   <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
     <t>02645250</t>
   </si>
   <si>
@@ -736,21 +733,21 @@
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
     <t>chuẩn bị kiểm kê</t>
   </si>
   <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
     <t>lắp đặt thiết bị</t>
   </si>
   <si>
@@ -778,39 +775,36 @@
     <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
   </si>
   <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
     <t>ca1 tăng ca sản xuất</t>
   </si>
   <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
-  </si>
-  <si>
     <t>02243654</t>
   </si>
   <si>
@@ -853,24 +847,24 @@
     <t>16/09/2026 15:30:00</t>
   </si>
   <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
     <t>21/09/2026 20:30:00</t>
   </si>
   <si>
     <t>21/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>02644066</t>
   </si>
   <si>
@@ -883,10 +877,10 @@
     <t>23/09/2026 15:30:00</t>
   </si>
   <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
     <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
   </si>
   <si>
     <t>21/09/2026 15:30:00</t>
@@ -1478,47 +1472,47 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="J5" s="8">
+        <v>120</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="8">
-        <v>480</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="M5" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="8" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>27</v>
@@ -1526,40 +1520,40 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="J6" s="8">
         <v>120</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1574,47 +1568,47 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="J7" s="8">
         <v>120</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M7" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="8" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>27</v>
@@ -1622,10 +1616,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1634,7 +1628,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -1643,19 +1637,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J8" s="8">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -1670,10 +1664,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -1682,7 +1676,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -1691,19 +1685,19 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J9" s="8">
         <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1718,10 +1712,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1730,7 +1724,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -1739,19 +1733,19 @@
         <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J10" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1761,15 +1755,15 @@
         <v>26</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1778,7 +1772,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1787,19 +1781,19 @@
         <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J11" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1814,47 +1808,47 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="J12" s="8">
         <v>120</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M12" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="8" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>27</v>
@@ -1862,10 +1856,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1874,28 +1868,28 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="J13" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1910,19 +1904,19 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1931,19 +1925,19 @@
         <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J14" s="8">
         <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1958,10 +1952,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -1970,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -1979,26 +1973,26 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="8">
+        <v>480</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="8">
-        <v>120</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="L15" s="8" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="M15" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="8" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>27</v>
@@ -2006,20 +2000,20 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
       </c>
@@ -2027,19 +2021,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J16" s="8">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -2054,20 +2048,20 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
       </c>
@@ -2075,19 +2069,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J17" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -2102,20 +2096,20 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
       </c>
@@ -2123,19 +2117,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J18" s="8">
         <v>480</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="M18" s="8">
         <v>0</v>
@@ -2150,10 +2144,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -2162,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>22</v>
@@ -2171,26 +2165,26 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J19" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M19" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="8" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>27</v>
@@ -2198,10 +2192,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -2210,28 +2204,28 @@
         <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="J20" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="M20" s="8">
         <v>0</v>
@@ -2246,10 +2240,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -2267,19 +2261,19 @@
         <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="J21" s="8">
         <v>480</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -2294,19 +2288,19 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="E22" s="7" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -2315,19 +2309,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="J22" s="8">
         <v>480</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -2342,10 +2336,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -2354,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>22</v>
@@ -2363,19 +2357,19 @@
         <v>23</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="J23" s="8">
         <v>480</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="M23" s="8">
         <v>0</v>
@@ -2390,10 +2384,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -2402,7 +2396,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>22</v>
@@ -2411,19 +2405,19 @@
         <v>23</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="J24" s="8">
         <v>480</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -2438,10 +2432,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
@@ -2450,7 +2444,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>22</v>
@@ -2459,19 +2453,19 @@
         <v>23</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="J25" s="8">
         <v>480</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -2486,10 +2480,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -2498,7 +2492,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>22</v>
@@ -2507,19 +2501,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J26" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -2534,10 +2528,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -2546,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -2555,19 +2549,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="J27" s="8">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2582,10 +2576,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2594,7 +2588,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2603,19 +2597,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="J28" s="8">
         <v>480</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2630,10 +2624,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
@@ -2642,7 +2636,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2651,19 +2645,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J29" s="8">
         <v>120</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -2678,10 +2672,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2690,7 +2684,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2699,26 +2693,26 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J30" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="M30" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P30" s="4" t="s">
         <v>27</v>
@@ -2726,10 +2720,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -2738,7 +2732,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
@@ -2747,19 +2741,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="J31" s="4">
         <v>480</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2774,10 +2768,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -2786,7 +2780,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2795,19 +2789,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="J32" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2817,15 +2811,15 @@
         <v>26</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -2834,7 +2828,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2843,19 +2837,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="J33" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2865,7 +2859,7 @@
         <v>26</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -2882,7 +2876,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>22</v>
@@ -2891,19 +2885,19 @@
         <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J34" s="4">
         <v>480</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2918,10 +2912,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2930,7 +2924,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2939,19 +2933,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="J35" s="4">
         <v>480</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2966,10 +2960,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -2978,7 +2972,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>22</v>
@@ -2987,19 +2981,19 @@
         <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J36" s="4">
         <v>480</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="M36" s="4">
         <v>0</v>
@@ -3014,10 +3008,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -3026,7 +3020,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>22</v>
@@ -3035,19 +3029,19 @@
         <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J37" s="4">
         <v>120</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M37" s="4">
         <v>0</v>
@@ -3062,10 +3056,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -3074,7 +3068,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -3083,19 +3077,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="J38" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -3110,19 +3104,19 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -3131,19 +3125,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="J39" s="4">
         <v>480</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -3158,10 +3152,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -3170,7 +3164,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>22</v>
@@ -3179,19 +3173,19 @@
         <v>23</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="J40" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="M40" s="4">
         <v>0</v>
@@ -3206,19 +3200,19 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>22</v>
@@ -3227,19 +3221,19 @@
         <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="J41" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -3254,10 +3248,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -3266,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>22</v>
@@ -3275,19 +3269,19 @@
         <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J42" s="4">
         <v>480</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -3302,10 +3296,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -3314,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -3323,19 +3317,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J43" s="4">
         <v>120</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -3350,10 +3344,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -3362,7 +3356,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -3371,19 +3365,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="J44" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -3398,10 +3392,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -3410,7 +3404,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>22</v>
@@ -3419,19 +3413,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J45" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -3446,40 +3440,40 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="F46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="I46" s="4" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="J46" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -3494,10 +3488,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -3506,7 +3500,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>22</v>
@@ -3515,19 +3509,19 @@
         <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="J47" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3542,10 +3536,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -3554,7 +3548,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>22</v>
@@ -3563,19 +3557,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="J48" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3590,10 +3584,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -3602,7 +3596,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>22</v>
@@ -3611,19 +3605,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="J49" s="4">
         <v>480</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3638,10 +3632,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -3650,7 +3644,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>22</v>
@@ -3659,19 +3653,19 @@
         <v>23</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="J50" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="M50" s="4">
         <v>0</v>
@@ -3686,10 +3680,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -3698,7 +3692,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>22</v>
@@ -3707,19 +3701,19 @@
         <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="J51" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -3734,10 +3728,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -3746,7 +3740,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -3755,19 +3749,19 @@
         <v>23</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="J52" s="4">
         <v>480</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="M52" s="4">
         <v>0</v>
@@ -3782,10 +3776,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
@@ -3794,7 +3788,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>22</v>
@@ -3803,19 +3797,19 @@
         <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="J53" s="4">
         <v>480</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="M53" s="4">
         <v>0</v>
@@ -3830,10 +3824,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>19</v>
@@ -3842,7 +3836,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>22</v>
@@ -3851,19 +3845,19 @@
         <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="J54" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -3878,10 +3872,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
@@ -3890,7 +3884,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>22</v>
@@ -3899,19 +3893,19 @@
         <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="J55" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -3926,10 +3920,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>19</v>
@@ -3938,7 +3932,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>22</v>
@@ -3947,19 +3941,19 @@
         <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="J56" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="M56" s="4">
         <v>0</v>
@@ -3974,10 +3968,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
@@ -3986,7 +3980,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>22</v>
@@ -3995,19 +3989,19 @@
         <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="J57" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -4022,10 +4016,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
@@ -4034,7 +4028,7 @@
         <v>20</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>22</v>
@@ -4043,19 +4037,19 @@
         <v>23</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="J58" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -4070,10 +4064,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
@@ -4082,7 +4076,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>22</v>
@@ -4091,19 +4085,19 @@
         <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J59" s="4">
         <v>480</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="M59" s="4">
         <v>0</v>
@@ -4118,10 +4112,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
@@ -4130,7 +4124,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>22</v>
@@ -4139,19 +4133,19 @@
         <v>23</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="J60" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="M60" s="4">
         <v>0</v>
@@ -4166,10 +4160,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
@@ -4178,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>22</v>
@@ -4187,19 +4181,19 @@
         <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="J61" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="M61" s="4">
         <v>0</v>
@@ -4214,10 +4208,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
@@ -4226,7 +4220,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>22</v>
@@ -4235,19 +4229,19 @@
         <v>23</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="J62" s="4">
         <v>90</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="M62" s="4">
         <v>0</v>
@@ -4262,10 +4256,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
@@ -4274,7 +4268,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>22</v>
@@ -4283,19 +4277,19 @@
         <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="J63" s="4">
         <v>480</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="M63" s="4">
         <v>0</v>
@@ -4310,10 +4304,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
@@ -4322,7 +4316,7 @@
         <v>20</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>22</v>
@@ -4331,19 +4325,19 @@
         <v>23</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="J64" s="4">
         <v>90</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="M64" s="4">
         <v>0</v>
@@ -4353,15 +4347,15 @@
         <v>26</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>19</v>
@@ -4370,7 +4364,7 @@
         <v>20</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>22</v>
@@ -4379,16 +4373,16 @@
         <v>23</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>64</v>
       </c>
       <c r="J65" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>64</v>
@@ -4406,10 +4400,10 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>19</v>
@@ -4418,7 +4412,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>22</v>
@@ -4427,19 +4421,19 @@
         <v>23</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J66" s="4">
         <v>480</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M66" s="4">
         <v>0</v>
@@ -4454,10 +4448,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>19</v>
@@ -4466,7 +4460,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>22</v>
@@ -4475,19 +4469,19 @@
         <v>23</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="J67" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="M67" s="4">
         <v>0</v>
@@ -4502,10 +4496,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>19</v>
@@ -4514,7 +4508,7 @@
         <v>20</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>22</v>
@@ -4523,19 +4517,19 @@
         <v>23</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="J68" s="4">
         <v>480</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="M68" s="4">
         <v>0</v>
@@ -4550,10 +4544,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>19</v>
@@ -4562,7 +4556,7 @@
         <v>20</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>22</v>
@@ -4571,19 +4565,19 @@
         <v>23</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J69" s="4">
         <v>480</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="M69" s="4">
         <v>0</v>
@@ -4598,10 +4592,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>19</v>
@@ -4610,7 +4604,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>22</v>
@@ -4619,19 +4613,19 @@
         <v>23</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="J70" s="4">
         <v>90</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="M70" s="4">
         <v>0</v>
@@ -4646,11 +4640,11 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
@@ -4658,7 +4652,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>22</v>
@@ -4667,19 +4661,19 @@
         <v>23</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="J71" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="M71" s="4">
         <v>0</v>
@@ -4694,11 +4688,11 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="C72" s="3" t="s">
         <v>19</v>
       </c>
@@ -4706,7 +4700,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>22</v>
@@ -4715,19 +4709,19 @@
         <v>23</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="J72" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="M72" s="4">
         <v>0</v>
@@ -4742,10 +4736,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>19</v>
@@ -4763,19 +4757,19 @@
         <v>23</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="J73" s="4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="M73" s="4">
         <v>0</v>
@@ -4790,10 +4784,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>19</v>
@@ -4811,19 +4805,19 @@
         <v>23</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="J74" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="M74" s="4">
         <v>0</v>
@@ -4838,10 +4832,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>19</v>
@@ -4850,7 +4844,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>22</v>
@@ -4859,19 +4853,19 @@
         <v>23</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I75" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J75" s="4">
         <v>120</v>
       </c>
-      <c r="J75" s="4">
-        <v>180</v>
-      </c>
       <c r="K75" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M75" s="4">
         <v>0</v>
@@ -4886,10 +4880,10 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>19</v>
@@ -4898,7 +4892,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>22</v>
@@ -4907,16 +4901,16 @@
         <v>23</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>183</v>
       </c>
       <c r="J76" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>183</v>
@@ -4934,10 +4928,10 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>19</v>
@@ -4946,7 +4940,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>22</v>
@@ -4955,19 +4949,19 @@
         <v>23</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="J77" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="M77" s="4">
         <v>0</v>
@@ -4982,10 +4976,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>19</v>
@@ -4994,7 +4988,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>22</v>
@@ -5003,19 +4997,19 @@
         <v>23</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="J78" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="M78" s="4">
         <v>0</v>
@@ -5030,10 +5024,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>19</v>
@@ -5042,7 +5036,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>22</v>
@@ -5051,19 +5045,19 @@
         <v>23</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="J79" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="M79" s="4">
         <v>0</v>
@@ -5073,15 +5067,15 @@
         <v>26</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>19</v>
@@ -5090,7 +5084,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -5099,19 +5093,19 @@
         <v>23</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="J80" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="M80" s="4">
         <v>0</v>
@@ -5126,10 +5120,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>19</v>
@@ -5138,7 +5132,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>22</v>
@@ -5147,19 +5141,19 @@
         <v>23</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J81" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="M81" s="4">
         <v>0</v>
@@ -5174,10 +5168,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>19</v>
@@ -5186,7 +5180,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>22</v>
@@ -5195,19 +5189,19 @@
         <v>23</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J82" s="4">
         <v>90</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M82" s="4">
         <v>0</v>
@@ -5222,10 +5216,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>19</v>
@@ -5234,7 +5228,7 @@
         <v>20</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>22</v>
@@ -5243,19 +5237,19 @@
         <v>23</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J83" s="4">
         <v>90</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M83" s="4">
         <v>0</v>
@@ -5270,10 +5264,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>19</v>
@@ -5282,7 +5276,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>22</v>
@@ -5291,19 +5285,19 @@
         <v>23</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>194</v>
+        <v>30</v>
       </c>
       <c r="J84" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>194</v>
+        <v>30</v>
       </c>
       <c r="M84" s="4">
         <v>0</v>
@@ -5318,40 +5312,40 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="J85" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M85" s="4">
         <v>0</v>
@@ -5366,10 +5360,10 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>19</v>
@@ -5378,7 +5372,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>22</v>
@@ -5387,19 +5381,19 @@
         <v>23</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="J86" s="4">
         <v>90</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="M86" s="4">
         <v>0</v>
@@ -5414,40 +5408,40 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I87" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="J87" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="M87" s="4">
         <v>0</v>
@@ -5462,19 +5456,19 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>22</v>
@@ -5483,19 +5477,19 @@
         <v>23</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J88" s="4">
         <v>480</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M88" s="4">
         <v>0</v>
@@ -5510,40 +5504,40 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="3" t="s">
+      <c r="I89" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="J89" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>25</v>
+        <v>202</v>
       </c>
       <c r="M89" s="4">
         <v>0</v>
@@ -5558,19 +5552,19 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>22</v>
@@ -5579,19 +5573,19 @@
         <v>23</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="J90" s="4">
         <v>480</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="M90" s="4">
         <v>0</v>
@@ -5606,20 +5600,20 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>22</v>
       </c>
@@ -5627,26 +5621,26 @@
         <v>23</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J91" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="M91" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3"/>
       <c r="O91" s="4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="P91" s="4" t="s">
         <v>27</v>
@@ -5654,11 +5648,11 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="3" t="s">
         <v>19</v>
       </c>
@@ -5666,7 +5660,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>22</v>
@@ -5675,19 +5669,19 @@
         <v>23</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="J92" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="M92" s="4">
         <v>0</v>
@@ -5702,11 +5696,11 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C93" s="3" t="s">
         <v>19</v>
       </c>
@@ -5714,7 +5708,7 @@
         <v>20</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>22</v>
@@ -5723,19 +5717,19 @@
         <v>23</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J93" s="4">
         <v>480</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="M93" s="4">
         <v>0</v>
@@ -5750,11 +5744,11 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C94" s="3" t="s">
         <v>19</v>
       </c>
@@ -5762,7 +5756,7 @@
         <v>20</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>22</v>
@@ -5771,19 +5765,19 @@
         <v>23</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="J94" s="4">
         <v>120</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="M94" s="4">
         <v>0</v>
@@ -5798,11 +5792,11 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C95" s="3" t="s">
         <v>19</v>
       </c>
@@ -5810,7 +5804,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>22</v>
@@ -5819,19 +5813,19 @@
         <v>23</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="J95" s="4">
         <v>120</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="M95" s="4">
         <v>0</v>
@@ -5846,11 +5840,11 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C96" s="3" t="s">
         <v>19</v>
       </c>
@@ -5858,7 +5852,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>22</v>
@@ -5867,26 +5861,26 @@
         <v>23</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="J96" s="4">
         <v>120</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M96" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P96" s="4" t="s">
         <v>27</v>
@@ -5894,20 +5888,20 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="F97" s="3" t="s">
         <v>22</v>
       </c>
@@ -5915,19 +5909,19 @@
         <v>23</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J97" s="4">
         <v>480</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="M97" s="4">
         <v>0</v>
@@ -5942,20 +5936,20 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="F98" s="3" t="s">
         <v>22</v>
       </c>
@@ -5963,19 +5957,19 @@
         <v>23</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="J98" s="4">
         <v>480</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="M98" s="4">
         <v>0</v>
@@ -5990,11 +5984,11 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C99" s="3" t="s">
         <v>19</v>
       </c>
@@ -6002,7 +5996,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>22</v>
@@ -6011,19 +6005,19 @@
         <v>23</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J99" s="4">
         <v>480</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="M99" s="4">
         <v>0</v>
@@ -6038,20 +6032,20 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>22</v>
       </c>
@@ -6059,19 +6053,19 @@
         <v>23</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J100" s="4">
         <v>480</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M100" s="4">
         <v>0</v>
@@ -6086,20 +6080,20 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>22</v>
       </c>
@@ -6107,19 +6101,19 @@
         <v>23</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="J101" s="4">
         <v>480</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M101" s="4">
         <v>0</v>
@@ -6134,11 +6128,11 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="C102" s="3" t="s">
         <v>19</v>
       </c>
@@ -6146,7 +6140,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>22</v>
@@ -6155,19 +6149,19 @@
         <v>23</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J102" s="4">
         <v>480</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M102" s="4">
         <v>0</v>
@@ -6182,10 +6176,10 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>19</v>
@@ -6194,7 +6188,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>22</v>
@@ -6203,19 +6197,19 @@
         <v>23</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="J103" s="4">
         <v>480</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="M103" s="4">
         <v>0</v>
@@ -6230,20 +6224,20 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="F104" s="3" t="s">
         <v>22</v>
       </c>
@@ -6251,19 +6245,19 @@
         <v>23</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="J104" s="4">
         <v>480</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="M104" s="4">
         <v>0</v>
@@ -6278,10 +6272,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>19</v>
@@ -6290,7 +6284,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>50</v>
+        <v>227</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>22</v>
@@ -6299,19 +6293,19 @@
         <v>23</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J105" s="4">
         <v>480</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M105" s="4">
         <v>0</v>
@@ -6326,20 +6320,20 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="F106" s="3" t="s">
         <v>22</v>
       </c>
@@ -6347,19 +6341,19 @@
         <v>23</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="J106" s="4">
         <v>480</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="M106" s="4">
         <v>0</v>
@@ -6374,20 +6368,20 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="F107" s="3" t="s">
         <v>22</v>
       </c>
@@ -6395,19 +6389,19 @@
         <v>23</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J107" s="4">
         <v>90</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="M107" s="4">
         <v>0</v>
@@ -6422,11 +6416,11 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="C108" s="3" t="s">
         <v>19</v>
       </c>
@@ -6434,7 +6428,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>22</v>
@@ -6443,19 +6437,19 @@
         <v>23</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J108" s="4">
         <v>480</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M108" s="4">
         <v>0</v>
@@ -6470,11 +6464,11 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="C109" s="3" t="s">
         <v>19</v>
       </c>
@@ -6482,7 +6476,7 @@
         <v>20</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>22</v>
@@ -6491,19 +6485,19 @@
         <v>23</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="J109" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="M109" s="4">
         <v>0</v>
@@ -6518,10 +6512,10 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>19</v>
@@ -6539,19 +6533,19 @@
         <v>23</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="J110" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="M110" s="4">
         <v>0</v>
@@ -6566,11 +6560,11 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="C111" s="3" t="s">
         <v>19</v>
       </c>
@@ -6578,28 +6572,28 @@
         <v>20</v>
       </c>
       <c r="E111" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F111" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="4" t="s">
+      <c r="I111" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="I111" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="J111" s="4">
         <v>90</v>
       </c>
       <c r="K111" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L111" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="M111" s="4">
         <v>0</v>
@@ -6614,40 +6608,40 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="F112" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="J112" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="M112" s="4">
         <v>0</v>
@@ -6662,40 +6656,40 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="F113" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="J113" s="4">
         <v>480</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="M113" s="4">
         <v>0</v>
@@ -6710,40 +6704,40 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>242</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="J114" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="M114" s="4">
         <v>0</v>
@@ -6758,40 +6752,40 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="C115" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>243</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J115" s="4">
         <v>480</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="M115" s="4">
         <v>0</v>
@@ -6806,40 +6800,40 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="J116" s="4">
         <v>480</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="M116" s="4">
         <v>0</v>
@@ -6854,40 +6848,40 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="F117" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J117" s="4">
         <v>480</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="M117" s="4">
         <v>0</v>
@@ -6902,40 +6896,40 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="C118" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="F118" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J118" s="4">
         <v>480</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="M118" s="4">
         <v>0</v>
@@ -6950,40 +6944,40 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="C119" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J119" s="4">
         <v>480</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="M119" s="4">
         <v>0</v>
@@ -6998,40 +6992,40 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="C120" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="J120" s="4">
         <v>480</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M120" s="4">
         <v>0</v>
@@ -7046,40 +7040,40 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="F121" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="J121" s="4">
         <v>480</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="M121" s="4">
         <v>0</v>
@@ -7094,40 +7088,40 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J122" s="4">
         <v>480</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="M122" s="4">
         <v>0</v>
@@ -7142,40 +7136,40 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="J123" s="4">
         <v>480</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="M123" s="4">
         <v>0</v>
@@ -7190,40 +7184,40 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J124" s="4">
         <v>120</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M124" s="4">
         <v>0</v>
@@ -7233,45 +7227,45 @@
         <v>26</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>260</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="F125" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="J125" s="4">
         <v>480</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="M125" s="4">
         <v>0</v>
@@ -7286,40 +7280,40 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J126" s="4">
         <v>480</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M126" s="4">
         <v>0</v>
@@ -7334,40 +7328,40 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="J127" s="4">
         <v>480</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M127" s="4">
         <v>0</v>
@@ -7382,40 +7376,40 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E128" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="F128" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="J128" s="4">
         <v>480</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M128" s="4">
         <v>0</v>
@@ -7430,40 +7424,40 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="F129" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J129" s="4">
         <v>480</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M129" s="4">
         <v>0</v>
@@ -7478,40 +7472,40 @@
     </row>
     <row r="130">
       <c r="A130" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F130" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J130" s="4">
         <v>90</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="M130" s="4">
         <v>0</v>
@@ -7526,40 +7520,40 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E131" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F131" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H131" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I131" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="I131" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="J131" s="4">
         <v>90</v>
       </c>
       <c r="K131" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="L131" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="L131" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="M131" s="4">
         <v>0</v>
@@ -7574,40 +7568,40 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F132" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="J132" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="M132" s="4">
         <v>0</v>
@@ -7622,40 +7616,40 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E133" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F133" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="J133" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="M133" s="4">
         <v>0</v>
@@ -7670,40 +7664,40 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="J134" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="M134" s="4">
         <v>0</v>
@@ -7718,40 +7712,40 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="I135" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="J135" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="M135" s="4">
         <v>0</v>
@@ -7766,40 +7760,40 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="J136" s="4">
         <v>480</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="M136" s="4">
         <v>0</v>
@@ -7814,40 +7808,40 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E137" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F137" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="J137" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="M137" s="4">
         <v>0</v>
@@ -7862,40 +7856,40 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E138" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="F138" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="J138" s="4">
         <v>90</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="M138" s="4">
         <v>0</v>
@@ -7910,40 +7904,40 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="J139" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="M139" s="4">
         <v>0</v>
@@ -7958,40 +7952,40 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="F140" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I140" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I140" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="J140" s="4">
         <v>90</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>46</v>
+        <v>274</v>
       </c>
       <c r="M140" s="4">
         <v>0</v>
@@ -8006,40 +8000,40 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E141" s="3" t="s">
+      <c r="F141" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I141" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="I141" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="J141" s="4">
         <v>90</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M141" s="4">
         <v>0</v>
@@ -8054,40 +8048,40 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F142" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>89</v>
+        <v>276</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="J142" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>89</v>
+        <v>276</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="M142" s="4">
         <v>0</v>
@@ -8102,40 +8096,40 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E143" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F143" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>277</v>
+        <v>59</v>
       </c>
       <c r="J143" s="4">
         <v>90</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>277</v>
+        <v>59</v>
       </c>
       <c r="M143" s="4">
         <v>0</v>
@@ -8150,40 +8144,40 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E144" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F144" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>278</v>
+        <v>25</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="J144" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>278</v>
+        <v>25</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="M144" s="4">
         <v>0</v>
@@ -8198,40 +8192,40 @@
     </row>
     <row r="145">
       <c r="A145" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F145" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J145" s="4">
         <v>90</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M145" s="4">
         <v>0</v>
@@ -8246,40 +8240,40 @@
     </row>
     <row r="146">
       <c r="A146" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F146" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>49</v>
+        <v>279</v>
       </c>
       <c r="J146" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>49</v>
+        <v>279</v>
       </c>
       <c r="M146" s="4">
         <v>0</v>
@@ -8294,28 +8288,28 @@
     </row>
     <row r="147">
       <c r="A147" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E147" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F147" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>281</v>
@@ -8324,7 +8318,7 @@
         <v>90</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="L147" s="4" t="s">
         <v>281</v>
@@ -8342,40 +8336,40 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F148" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>283</v>
+        <v>72</v>
       </c>
       <c r="J148" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>283</v>
+        <v>72</v>
       </c>
       <c r="M148" s="4">
         <v>0</v>
@@ -8385,45 +8379,45 @@
         <v>26</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>260</v>
+        <v>27</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="F149" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I149" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I149" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="J149" s="4">
         <v>90</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>155</v>
+        <v>259</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="M149" s="4">
         <v>0</v>
@@ -8438,40 +8432,40 @@
     </row>
     <row r="150">
       <c r="A150" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E150" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>286</v>
-      </c>
       <c r="F150" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>287</v>
+        <v>142</v>
       </c>
       <c r="J150" s="4">
         <v>90</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>287</v>
+        <v>142</v>
       </c>
       <c r="M150" s="4">
         <v>0</v>
@@ -8481,45 +8475,45 @@
         <v>26</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>260</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>286</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="J151" s="4">
         <v>90</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="M151" s="4">
         <v>0</v>
@@ -8534,40 +8528,40 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E152" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B152" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="F152" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="J152" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="M152" s="4">
         <v>0</v>
@@ -8582,40 +8576,40 @@
     </row>
     <row r="153">
       <c r="A153" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="J153" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="M153" s="4">
         <v>0</v>
@@ -8625,45 +8619,45 @@
         <v>26</v>
       </c>
       <c r="P153" s="4" t="s">
-        <v>260</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="J154" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="M154" s="4">
         <v>0</v>
@@ -8678,40 +8672,40 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E155" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B155" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="F155" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H155" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G155" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="I155" s="4" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="J155" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
@@ -8726,40 +8720,40 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E156" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>286</v>
-      </c>
       <c r="F156" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J156" s="4">
         <v>90</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M156" s="4">
         <v>0</v>
@@ -8774,40 +8768,40 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J157" s="4">
         <v>90</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M157" s="4">
         <v>0</v>
